--- a/Excel/ESP32-ADC-Linearity-Tester.xlsx
+++ b/Excel/ESP32-ADC-Linearity-Tester.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -21,17 +24,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>v_in</t>
-  </si>
-  <si>
-    <t>adc_value</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -82,6 +74,3168 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" cap="none" baseline="0"/>
+              <a:t>ESP32 ADC Calibration Curve &amp; 4th-Degree Polynomial Model</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ar-SA"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]chart!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mean</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="4"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.3576492593598216E-2"/>
+                  <c:y val="-3.7719574668814072E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="lt1">
+                            <a:lumMod val="75000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="ar-SA" sz="800" b="0" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="accent6"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>y = 26.512x</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="ar-SA" sz="800" b="0" baseline="30000">
+                        <a:solidFill>
+                          <a:schemeClr val="accent6"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>4</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="ar-SA" sz="800" b="0" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="accent6"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t> - 149.48x</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="ar-SA" sz="800" b="0" baseline="30000">
+                        <a:solidFill>
+                          <a:schemeClr val="accent6"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>3</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="ar-SA" sz="800" b="0" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="accent6"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t> + 321.98x</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="ar-SA" sz="800" b="0" baseline="30000">
+                        <a:solidFill>
+                          <a:schemeClr val="accent6"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>2</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="ar-SA" sz="800" b="0" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="accent6"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t> + 915.38x - 67.233</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="ar-SA" sz="800" b="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                    </a:endParaRPr>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="75000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ar-SA"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>[1]chart!$A$2:$A$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.105</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.216</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.33400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.40899999999999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.50800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.60299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.72699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.83699999999999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.94599999999999995</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.135</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.24</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.355</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.4790000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.619</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.7210000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.847</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.98</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.044</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.1179999999999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.226</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.3479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.444</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.556</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.677</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.7959999999999998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.851</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.9449999999999998</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.04</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.1120000000000001</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.21</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>[1]chart!$B$2:$B$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>108.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>247.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>337</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>456.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>573.79999999999995</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>719.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>852.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>988.6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1071.4000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1219.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1352.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1487.8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1648.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1814.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1935</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2096.6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2254.6</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2330.4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2422.4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2556.1999999999998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2705.4</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2829.2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2982</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3154.2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3344.4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3436.6</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3627.8</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3826</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3996.2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4095</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>4095</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="-1041981408"/>
+        <c:axId val="-1041980320"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="-1041981408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:noFill/>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ar-SA"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-1041980320"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="-1041980320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ar-SA"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-1041981408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ar-SA"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ar-SA"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]chart!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Voltage(V)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="4"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout/>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ar-SA"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>[1]chart!$K$2:$K$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>108.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>247.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>337</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>456.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>573.79999999999995</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>719.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>852.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>988.6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1071.4000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1219.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1352.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1487.8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1648.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1814.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1935</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2096.6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2254.6</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2330.4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2422.4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2556.1999999999998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2705.4</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2829.2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2982</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3154.2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3344.4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3436.6</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3627.8</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3826</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3996.2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4095</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>4095</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>[1]chart!$L$2:$L$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.105</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.216</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.33400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.40899999999999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.50800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.60299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.72699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.83699999999999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.94599999999999995</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.135</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.24</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.355</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.4790000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.619</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.7210000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.847</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.98</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.044</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.1179999999999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.226</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.3479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.444</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.556</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.677</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.7959999999999998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.851</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.9449999999999998</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.04</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.1120000000000001</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.21</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="-1041976512"/>
+        <c:axId val="-1250102480"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="-1041976512"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ar-SA"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-1250102480"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="-1250102480"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ar-SA"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-1041976512"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ar-SA"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="245">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="3"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="adc_test_report   01072026"/>
+      <sheetName val="chart"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>Voltage(V)</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>Mean</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="B2">
+            <v>0</v>
+          </cell>
+          <cell r="D2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>0.105</v>
+          </cell>
+          <cell r="D3">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4">
+            <v>0.216</v>
+          </cell>
+          <cell r="D4">
+            <v>108.2</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5">
+            <v>0.33400000000000002</v>
+          </cell>
+          <cell r="D5">
+            <v>247.6</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6">
+            <v>0.40899999999999997</v>
+          </cell>
+          <cell r="D6">
+            <v>337</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>0.50800000000000001</v>
+          </cell>
+          <cell r="D7">
+            <v>456.2</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8">
+            <v>0.60299999999999998</v>
+          </cell>
+          <cell r="D8">
+            <v>573.79999999999995</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9">
+            <v>0.72699999999999998</v>
+          </cell>
+          <cell r="D9">
+            <v>719.2</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10">
+            <v>0.83699999999999997</v>
+          </cell>
+          <cell r="D10">
+            <v>852.6</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11">
+            <v>0.94599999999999995</v>
+          </cell>
+          <cell r="D11">
+            <v>988.6</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12">
+            <v>1</v>
+          </cell>
+          <cell r="D12">
+            <v>1071.4000000000001</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13">
+            <v>1.135</v>
+          </cell>
+          <cell r="D13">
+            <v>1219.2</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14">
+            <v>1.24</v>
+          </cell>
+          <cell r="D14">
+            <v>1352.6</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15">
+            <v>1.355</v>
+          </cell>
+          <cell r="D15">
+            <v>1487.8</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16">
+            <v>1.4790000000000001</v>
+          </cell>
+          <cell r="D16">
+            <v>1648.2</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17">
+            <v>1.619</v>
+          </cell>
+          <cell r="D17">
+            <v>1814.2</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18">
+            <v>1.7210000000000001</v>
+          </cell>
+          <cell r="D18">
+            <v>1935</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19">
+            <v>1.847</v>
+          </cell>
+          <cell r="D19">
+            <v>2096.6</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20">
+            <v>1.98</v>
+          </cell>
+          <cell r="D20">
+            <v>2254.6</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21">
+            <v>2.044</v>
+          </cell>
+          <cell r="D21">
+            <v>2330.4</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22">
+            <v>2.1179999999999999</v>
+          </cell>
+          <cell r="D22">
+            <v>2422.4</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23">
+            <v>2.226</v>
+          </cell>
+          <cell r="D23">
+            <v>2556.1999999999998</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24">
+            <v>2.3479999999999999</v>
+          </cell>
+          <cell r="D24">
+            <v>2705.4</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25">
+            <v>2.444</v>
+          </cell>
+          <cell r="D25">
+            <v>2829.2</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26">
+            <v>2.556</v>
+          </cell>
+          <cell r="D26">
+            <v>2982</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27">
+            <v>2.677</v>
+          </cell>
+          <cell r="D27">
+            <v>3154.2</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28">
+            <v>2.7959999999999998</v>
+          </cell>
+          <cell r="D28">
+            <v>3344.4</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29">
+            <v>2.851</v>
+          </cell>
+          <cell r="D29">
+            <v>3436.6</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30">
+            <v>2.9449999999999998</v>
+          </cell>
+          <cell r="D30">
+            <v>3627.8</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31">
+            <v>3.04</v>
+          </cell>
+          <cell r="D31">
+            <v>3826</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32">
+            <v>3.1120000000000001</v>
+          </cell>
+          <cell r="D32">
+            <v>3996.2</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33">
+            <v>3.21</v>
+          </cell>
+          <cell r="D33">
+            <v>4095</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34">
+            <v>3.3</v>
+          </cell>
+          <cell r="D34">
+            <v>4095</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>Mean</v>
+          </cell>
+          <cell r="L1" t="str">
+            <v>Voltage(V)</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>0</v>
+          </cell>
+          <cell r="B2">
+            <v>0</v>
+          </cell>
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="L2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>0.105</v>
+          </cell>
+          <cell r="B3">
+            <v>0</v>
+          </cell>
+          <cell r="K3">
+            <v>0</v>
+          </cell>
+          <cell r="L3">
+            <v>0.105</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>0.216</v>
+          </cell>
+          <cell r="B4">
+            <v>108.2</v>
+          </cell>
+          <cell r="K4">
+            <v>108.2</v>
+          </cell>
+          <cell r="L4">
+            <v>0.216</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>0.33400000000000002</v>
+          </cell>
+          <cell r="B5">
+            <v>247.6</v>
+          </cell>
+          <cell r="K5">
+            <v>247.6</v>
+          </cell>
+          <cell r="L5">
+            <v>0.33400000000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>0.40899999999999997</v>
+          </cell>
+          <cell r="B6">
+            <v>337</v>
+          </cell>
+          <cell r="K6">
+            <v>337</v>
+          </cell>
+          <cell r="L6">
+            <v>0.40899999999999997</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>0.50800000000000001</v>
+          </cell>
+          <cell r="B7">
+            <v>456.2</v>
+          </cell>
+          <cell r="K7">
+            <v>456.2</v>
+          </cell>
+          <cell r="L7">
+            <v>0.50800000000000001</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>0.60299999999999998</v>
+          </cell>
+          <cell r="B8">
+            <v>573.79999999999995</v>
+          </cell>
+          <cell r="K8">
+            <v>573.79999999999995</v>
+          </cell>
+          <cell r="L8">
+            <v>0.60299999999999998</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>0.72699999999999998</v>
+          </cell>
+          <cell r="B9">
+            <v>719.2</v>
+          </cell>
+          <cell r="K9">
+            <v>719.2</v>
+          </cell>
+          <cell r="L9">
+            <v>0.72699999999999998</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>0.83699999999999997</v>
+          </cell>
+          <cell r="B10">
+            <v>852.6</v>
+          </cell>
+          <cell r="K10">
+            <v>852.6</v>
+          </cell>
+          <cell r="L10">
+            <v>0.83699999999999997</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>0.94599999999999995</v>
+          </cell>
+          <cell r="B11">
+            <v>988.6</v>
+          </cell>
+          <cell r="K11">
+            <v>988.6</v>
+          </cell>
+          <cell r="L11">
+            <v>0.94599999999999995</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>1</v>
+          </cell>
+          <cell r="B12">
+            <v>1071.4000000000001</v>
+          </cell>
+          <cell r="K12">
+            <v>1071.4000000000001</v>
+          </cell>
+          <cell r="L12">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>1.135</v>
+          </cell>
+          <cell r="B13">
+            <v>1219.2</v>
+          </cell>
+          <cell r="K13">
+            <v>1219.2</v>
+          </cell>
+          <cell r="L13">
+            <v>1.135</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>1.24</v>
+          </cell>
+          <cell r="B14">
+            <v>1352.6</v>
+          </cell>
+          <cell r="K14">
+            <v>1352.6</v>
+          </cell>
+          <cell r="L14">
+            <v>1.24</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>1.355</v>
+          </cell>
+          <cell r="B15">
+            <v>1487.8</v>
+          </cell>
+          <cell r="K15">
+            <v>1487.8</v>
+          </cell>
+          <cell r="L15">
+            <v>1.355</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>1.4790000000000001</v>
+          </cell>
+          <cell r="B16">
+            <v>1648.2</v>
+          </cell>
+          <cell r="K16">
+            <v>1648.2</v>
+          </cell>
+          <cell r="L16">
+            <v>1.4790000000000001</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>1.619</v>
+          </cell>
+          <cell r="B17">
+            <v>1814.2</v>
+          </cell>
+          <cell r="K17">
+            <v>1814.2</v>
+          </cell>
+          <cell r="L17">
+            <v>1.619</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>1.7210000000000001</v>
+          </cell>
+          <cell r="B18">
+            <v>1935</v>
+          </cell>
+          <cell r="K18">
+            <v>1935</v>
+          </cell>
+          <cell r="L18">
+            <v>1.7210000000000001</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>1.847</v>
+          </cell>
+          <cell r="B19">
+            <v>2096.6</v>
+          </cell>
+          <cell r="K19">
+            <v>2096.6</v>
+          </cell>
+          <cell r="L19">
+            <v>1.847</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>1.98</v>
+          </cell>
+          <cell r="B20">
+            <v>2254.6</v>
+          </cell>
+          <cell r="K20">
+            <v>2254.6</v>
+          </cell>
+          <cell r="L20">
+            <v>1.98</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>2.044</v>
+          </cell>
+          <cell r="B21">
+            <v>2330.4</v>
+          </cell>
+          <cell r="K21">
+            <v>2330.4</v>
+          </cell>
+          <cell r="L21">
+            <v>2.044</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>2.1179999999999999</v>
+          </cell>
+          <cell r="B22">
+            <v>2422.4</v>
+          </cell>
+          <cell r="K22">
+            <v>2422.4</v>
+          </cell>
+          <cell r="L22">
+            <v>2.1179999999999999</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>2.226</v>
+          </cell>
+          <cell r="B23">
+            <v>2556.1999999999998</v>
+          </cell>
+          <cell r="K23">
+            <v>2556.1999999999998</v>
+          </cell>
+          <cell r="L23">
+            <v>2.226</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>2.3479999999999999</v>
+          </cell>
+          <cell r="B24">
+            <v>2705.4</v>
+          </cell>
+          <cell r="K24">
+            <v>2705.4</v>
+          </cell>
+          <cell r="L24">
+            <v>2.3479999999999999</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>2.444</v>
+          </cell>
+          <cell r="B25">
+            <v>2829.2</v>
+          </cell>
+          <cell r="K25">
+            <v>2829.2</v>
+          </cell>
+          <cell r="L25">
+            <v>2.444</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>2.556</v>
+          </cell>
+          <cell r="B26">
+            <v>2982</v>
+          </cell>
+          <cell r="K26">
+            <v>2982</v>
+          </cell>
+          <cell r="L26">
+            <v>2.556</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>2.677</v>
+          </cell>
+          <cell r="B27">
+            <v>3154.2</v>
+          </cell>
+          <cell r="K27">
+            <v>3154.2</v>
+          </cell>
+          <cell r="L27">
+            <v>2.677</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>2.7959999999999998</v>
+          </cell>
+          <cell r="B28">
+            <v>3344.4</v>
+          </cell>
+          <cell r="K28">
+            <v>3344.4</v>
+          </cell>
+          <cell r="L28">
+            <v>2.7959999999999998</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>2.851</v>
+          </cell>
+          <cell r="B29">
+            <v>3436.6</v>
+          </cell>
+          <cell r="K29">
+            <v>3436.6</v>
+          </cell>
+          <cell r="L29">
+            <v>2.851</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>2.9449999999999998</v>
+          </cell>
+          <cell r="B30">
+            <v>3627.8</v>
+          </cell>
+          <cell r="K30">
+            <v>3627.8</v>
+          </cell>
+          <cell r="L30">
+            <v>2.9449999999999998</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>3.04</v>
+          </cell>
+          <cell r="B31">
+            <v>3826</v>
+          </cell>
+          <cell r="K31">
+            <v>3826</v>
+          </cell>
+          <cell r="L31">
+            <v>3.04</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>3.1120000000000001</v>
+          </cell>
+          <cell r="B32">
+            <v>3996.2</v>
+          </cell>
+          <cell r="K32">
+            <v>3996.2</v>
+          </cell>
+          <cell r="L32">
+            <v>3.1120000000000001</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>3.21</v>
+          </cell>
+          <cell r="B33">
+            <v>4095</v>
+          </cell>
+          <cell r="K33">
+            <v>4095</v>
+          </cell>
+          <cell r="L33">
+            <v>3.21</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>3.3</v>
+          </cell>
+          <cell r="B34">
+            <v>4095</v>
+          </cell>
+          <cell r="K34">
+            <v>4095</v>
+          </cell>
+          <cell r="L34">
+            <v>3.3</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -347,34 +3501,623 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="9.875" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" t="str">
+        <f>'[1]adc_test_report   01072026'!B1</f>
+        <v>Voltage(V)</v>
+      </c>
+      <c r="B1" t="str">
+        <f>'[1]adc_test_report   01072026'!D1</f>
+        <v>Mean</v>
+      </c>
+      <c r="K1" t="str">
+        <f>B1</f>
+        <v>Mean</v>
+      </c>
+      <c r="L1" t="str">
+        <f>A1</f>
+        <v>Voltage(V)</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <f>'[1]adc_test_report   01072026'!B2</f>
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2">
+        <f>'[1]adc_test_report   01072026'!D2</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f t="shared" ref="K2:K34" si="0">B2</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f t="shared" ref="L2:L34" si="1">A2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <f>'[1]adc_test_report   01072026'!B3</f>
+        <v>0.105</v>
+      </c>
+      <c r="B3">
+        <f>'[1]adc_test_report   01072026'!D3</f>
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="1"/>
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <f>'[1]adc_test_report   01072026'!B4</f>
+        <v>0.216</v>
+      </c>
+      <c r="B4">
+        <f>'[1]adc_test_report   01072026'!D4</f>
+        <v>108.2</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>108.2</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="1"/>
+        <v>0.216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <f>'[1]adc_test_report   01072026'!B5</f>
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="B5">
+        <f>'[1]adc_test_report   01072026'!D5</f>
+        <v>247.6</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>247.6</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="1"/>
+        <v>0.33400000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <f>'[1]adc_test_report   01072026'!B6</f>
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="B6">
+        <f>'[1]adc_test_report   01072026'!D6</f>
+        <v>337</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>337</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="1"/>
+        <v>0.40899999999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <f>'[1]adc_test_report   01072026'!B7</f>
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="B7">
+        <f>'[1]adc_test_report   01072026'!D7</f>
+        <v>456.2</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>456.2</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="1"/>
+        <v>0.50800000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <f>'[1]adc_test_report   01072026'!B8</f>
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="B8">
+        <f>'[1]adc_test_report   01072026'!D8</f>
+        <v>573.79999999999995</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>573.79999999999995</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="1"/>
+        <v>0.60299999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <f>'[1]adc_test_report   01072026'!B9</f>
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="B9">
+        <f>'[1]adc_test_report   01072026'!D9</f>
+        <v>719.2</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>719.2</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="1"/>
+        <v>0.72699999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <f>'[1]adc_test_report   01072026'!B10</f>
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="B10">
+        <f>'[1]adc_test_report   01072026'!D10</f>
+        <v>852.6</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>852.6</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="1"/>
+        <v>0.83699999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <f>'[1]adc_test_report   01072026'!B11</f>
+        <v>0.94599999999999995</v>
+      </c>
+      <c r="B11">
+        <f>'[1]adc_test_report   01072026'!D11</f>
+        <v>988.6</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>988.6</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="1"/>
+        <v>0.94599999999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <f>'[1]adc_test_report   01072026'!B12</f>
         <v>1</v>
       </c>
+      <c r="B12">
+        <f>'[1]adc_test_report   01072026'!D12</f>
+        <v>1071.4000000000001</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>1071.4000000000001</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <f>'[1]adc_test_report   01072026'!B13</f>
+        <v>1.135</v>
+      </c>
+      <c r="B13">
+        <f>'[1]adc_test_report   01072026'!D13</f>
+        <v>1219.2</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>1219.2</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="1"/>
+        <v>1.135</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>0.14000000000000001</v>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <f>'[1]adc_test_report   01072026'!B14</f>
+        <v>1.24</v>
+      </c>
+      <c r="B14">
+        <f>'[1]adc_test_report   01072026'!D14</f>
+        <v>1352.6</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>1352.6</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="1"/>
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <f>'[1]adc_test_report   01072026'!B15</f>
+        <v>1.355</v>
+      </c>
+      <c r="B15">
+        <f>'[1]adc_test_report   01072026'!D15</f>
+        <v>1487.8</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>1487.8</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>1.355</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <f>'[1]adc_test_report   01072026'!B16</f>
+        <v>1.4790000000000001</v>
+      </c>
+      <c r="B16">
+        <f>'[1]adc_test_report   01072026'!D16</f>
+        <v>1648.2</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>1648.2</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>1.4790000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <f>'[1]adc_test_report   01072026'!B17</f>
+        <v>1.619</v>
+      </c>
+      <c r="B17">
+        <f>'[1]adc_test_report   01072026'!D17</f>
+        <v>1814.2</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>1814.2</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="1"/>
+        <v>1.619</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <f>'[1]adc_test_report   01072026'!B18</f>
+        <v>1.7210000000000001</v>
+      </c>
+      <c r="B18">
+        <f>'[1]adc_test_report   01072026'!D18</f>
+        <v>1935</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>1935</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="1"/>
+        <v>1.7210000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <f>'[1]adc_test_report   01072026'!B19</f>
+        <v>1.847</v>
+      </c>
+      <c r="B19">
+        <f>'[1]adc_test_report   01072026'!D19</f>
+        <v>2096.6</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>2096.6</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="1"/>
+        <v>1.847</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <f>'[1]adc_test_report   01072026'!B20</f>
+        <v>1.98</v>
+      </c>
+      <c r="B20">
+        <f>'[1]adc_test_report   01072026'!D20</f>
+        <v>2254.6</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>2254.6</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="1"/>
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <f>'[1]adc_test_report   01072026'!B21</f>
+        <v>2.044</v>
+      </c>
+      <c r="B21">
+        <f>'[1]adc_test_report   01072026'!D21</f>
+        <v>2330.4</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="0"/>
+        <v>2330.4</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="1"/>
+        <v>2.044</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <f>'[1]adc_test_report   01072026'!B22</f>
+        <v>2.1179999999999999</v>
+      </c>
+      <c r="B22">
+        <f>'[1]adc_test_report   01072026'!D22</f>
+        <v>2422.4</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="0"/>
+        <v>2422.4</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="1"/>
+        <v>2.1179999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <f>'[1]adc_test_report   01072026'!B23</f>
+        <v>2.226</v>
+      </c>
+      <c r="B23">
+        <f>'[1]adc_test_report   01072026'!D23</f>
+        <v>2556.1999999999998</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="0"/>
+        <v>2556.1999999999998</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="1"/>
+        <v>2.226</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <f>'[1]adc_test_report   01072026'!B24</f>
+        <v>2.3479999999999999</v>
+      </c>
+      <c r="B24">
+        <f>'[1]adc_test_report   01072026'!D24</f>
+        <v>2705.4</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="0"/>
+        <v>2705.4</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="1"/>
+        <v>2.3479999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <f>'[1]adc_test_report   01072026'!B25</f>
+        <v>2.444</v>
+      </c>
+      <c r="B25">
+        <f>'[1]adc_test_report   01072026'!D25</f>
+        <v>2829.2</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="0"/>
+        <v>2829.2</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="1"/>
+        <v>2.444</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <f>'[1]adc_test_report   01072026'!B26</f>
+        <v>2.556</v>
+      </c>
+      <c r="B26">
+        <f>'[1]adc_test_report   01072026'!D26</f>
+        <v>2982</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="0"/>
+        <v>2982</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="1"/>
+        <v>2.556</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <f>'[1]adc_test_report   01072026'!B27</f>
+        <v>2.677</v>
+      </c>
+      <c r="B27">
+        <f>'[1]adc_test_report   01072026'!D27</f>
+        <v>3154.2</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="0"/>
+        <v>3154.2</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="1"/>
+        <v>2.677</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <f>'[1]adc_test_report   01072026'!B28</f>
+        <v>2.7959999999999998</v>
+      </c>
+      <c r="B28">
+        <f>'[1]adc_test_report   01072026'!D28</f>
+        <v>3344.4</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="0"/>
+        <v>3344.4</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="1"/>
+        <v>2.7959999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <f>'[1]adc_test_report   01072026'!B29</f>
+        <v>2.851</v>
+      </c>
+      <c r="B29">
+        <f>'[1]adc_test_report   01072026'!D29</f>
+        <v>3436.6</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="0"/>
+        <v>3436.6</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="1"/>
+        <v>2.851</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <f>'[1]adc_test_report   01072026'!B30</f>
+        <v>2.9449999999999998</v>
+      </c>
+      <c r="B30">
+        <f>'[1]adc_test_report   01072026'!D30</f>
+        <v>3627.8</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="0"/>
+        <v>3627.8</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="1"/>
+        <v>2.9449999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <f>'[1]adc_test_report   01072026'!B31</f>
+        <v>3.04</v>
+      </c>
+      <c r="B31">
+        <f>'[1]adc_test_report   01072026'!D31</f>
+        <v>3826</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="0"/>
+        <v>3826</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="1"/>
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <f>'[1]adc_test_report   01072026'!B32</f>
+        <v>3.1120000000000001</v>
+      </c>
+      <c r="B32">
+        <f>'[1]adc_test_report   01072026'!D32</f>
+        <v>3996.2</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="0"/>
+        <v>3996.2</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="1"/>
+        <v>3.1120000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <f>'[1]adc_test_report   01072026'!B33</f>
+        <v>3.21</v>
+      </c>
+      <c r="B33">
+        <f>'[1]adc_test_report   01072026'!D33</f>
+        <v>4095</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="0"/>
+        <v>4095</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="1"/>
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <f>'[1]adc_test_report   01072026'!B34</f>
+        <v>3.3</v>
+      </c>
+      <c r="B34">
+        <f>'[1]adc_test_report   01072026'!D34</f>
+        <v>4095</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="0"/>
+        <v>4095</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="1"/>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>